--- a/week3/manual_gold/688775_影石创新_gold.xlsx
+++ b/week3/manual_gold/688775_影石创新_gold.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,16 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>数据来源类型</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -502,6 +512,11 @@
           <t>2015年7月，北京岚锋以货币出资方式设立深圳岚锋，注册资本1000万元</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -542,6 +557,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>2020年2月股改，净资产52728.05万元按1:1.4647折为36000万股</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>直接披露</t>
         </is>
       </c>
     </row>
@@ -556,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,6 +630,11 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>时点说明</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -662,6 +687,11 @@
           <t>深圳岚锋设立时北京岚锋持股100%</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>公司设立后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -714,6 +744,11 @@
           <t>影石创新设立时北京岚锋持股29.9376%</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>整体变更为股份公司后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -766,6 +801,11 @@
           <t>EARN ACE持股13.3239%</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>整体变更为股份公司后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -818,6 +858,11 @@
           <t>QM101持股9.4001%</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>整体变更为股份公司后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -870,6 +915,11 @@
           <t>香港迅雷持股8.7327%</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>整体变更为股份公司后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -922,6 +972,11 @@
           <t>岚沣管理持股4.0667%</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>整体变更为股份公司后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -974,6 +1029,11 @@
           <t>华金同达持股3.9909%</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>整体变更为股份公司后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1026,6 +1086,11 @@
           <t>转让后北京岚锋持股29.9376%</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>本次股权转让完成后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1078,6 +1143,11 @@
           <t>EARN ACE持股13.3239%</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>本次股权转让完成后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1130,6 +1200,11 @@
           <t>QM101持股9.4001%</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>本次股权转让完成后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1180,6 +1255,11 @@
       <c r="J12" t="inlineStr">
         <is>
           <t>香港迅雷持股8.7327%</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>本次股权转让完成后的股权结构</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1371,6 +1451,11 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>转让类型</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1411,6 +1496,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>2023年3月，德朴投资以1462.7126万元的对价向汇智同裕转让股本287.0651万元</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>股东间转让</t>
         </is>
       </c>
     </row>
